--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -543,10 +543,10 @@
         <v>0.75</v>
       </c>
       <c r="G5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H5">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -569,10 +569,10 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -55,10 +55,10 @@
     <t>2006, 2010, 2014, 2018</t>
   </si>
   <si>
+    <t>PooledPollStructure</t>
+  </si>
+  <si>
     <t>PooledFullV11</t>
-  </si>
-  <si>
-    <t>PooledPollStructure</t>
   </si>
 </sst>
 </file>
@@ -456,19 +456,19 @@
         <v>13</v>
       </c>
       <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
         <v>0.25</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H2">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -482,7 +482,7 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -505,7 +505,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>0.25</v>
@@ -531,16 +531,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0.25</v>
       </c>
       <c r="E5">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
         <v>52</v>
@@ -557,7 +557,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>1</v>

--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -491,10 +491,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -569,10 +569,10 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -543,10 +543,10 @@
         <v>0.5</v>
       </c>
       <c r="G5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H5">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -569,10 +569,10 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -517,10 +517,10 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -543,10 +543,10 @@
         <v>0.5</v>
       </c>
       <c r="G5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -491,10 +491,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
+++ b/outputs/Block5B_Senate_2026_Fold_Summary.xlsx
@@ -491,10 +491,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -569,10 +569,10 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
